--- a/Assets/Samples/FirebaseDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/FirebaseDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -1399,11 +1399,31 @@
       <c r="U7" s="9" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>AppCustomConfig</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>拉取GM后台应用配置URL</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>HTTP_POST</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>GameServer</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>/v1/common/app-config</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="9" t="n"/>
